--- a/Data/CORS_coordinate_최종본.xlsx
+++ b/Data/CORS_coordinate_최종본.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C9ED2F-FC4C-C34A-9385-96BA60A25140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72600" yWindow="-15000" windowWidth="21600" windowHeight="37800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="72600" yWindow="-15000" windowWidth="21600" windowHeight="37800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="OBS_HEADER" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="B2" sheetId="5" r:id="rId5"/>
     <sheet name="C" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2671" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2676" uniqueCount="268">
   <si>
     <t>station</t>
   </si>
@@ -872,7 +872,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -889,7 +889,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -906,7 +906,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -938,7 +938,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -967,7 +967,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -984,7 +984,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
@@ -1076,7 +1076,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1088,12 +1088,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1270,157 +1270,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1444,7 +1446,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1595,7 +1597,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1619,9 +1621,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1645,7 +1647,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1680,7 +1682,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1698,7 +1700,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1723,7 +1725,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1759,34 +1761,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC227"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="10" width="12" customWidth="1"/>
-    <col min="11" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="17" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="15" style="8" customWidth="1"/>
-    <col min="22" max="22" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="true"/>
+    <col min="3" max="3" width="19.1640625" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="7.85546875" customWidth="true"/>
+    <col min="7" max="7" width="17" customWidth="true"/>
+    <col min="8" max="10" width="12" customWidth="true"/>
+    <col min="11" max="12" width="15" customWidth="true"/>
+    <col min="13" max="13" width="13" customWidth="true"/>
+    <col min="14" max="14" width="14.5" bestFit="true" customWidth="true"/>
+    <col min="15" max="15" width="13.33203125" bestFit="true" customWidth="true"/>
+    <col min="16" max="16" width="14.5" bestFit="true" customWidth="true"/>
+    <col min="17" max="17" width="14" bestFit="true" customWidth="true"/>
+    <col min="18" max="19" width="17" customWidth="true"/>
+    <col min="20" max="20" width="14" customWidth="true"/>
+    <col min="21" max="21" width="15" style="8" customWidth="true"/>
+    <col min="22" max="22" width="14" style="8" bestFit="true" customWidth="true"/>
+    <col min="23" max="23" width="14.5" style="8" bestFit="true" customWidth="true"/>
+    <col min="24" max="24" width="14" style="8" bestFit="true" customWidth="true"/>
+    <col min="25" max="25" width="13.83203125" bestFit="true" customWidth="true"/>
+    <col min="26" max="26" width="11.83203125" bestFit="true" customWidth="true"/>
+    <col min="27" max="27" width="14.5" bestFit="true" customWidth="true"/>
+    <col min="28" max="28" width="14" bestFit="true" customWidth="true"/>
+    <col min="5" max="6" width="12" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="20" thickBot="1">
+    <row r="1" ht="20" thickBot="true">
       <c r="N1" s="102" t="s">
         <v>261</v>
       </c>
@@ -1806,7 +1809,7 @@
       <c r="AB1" s="101"/>
       <c r="AC1" s="101"/>
     </row>
-    <row r="2" spans="1:29" ht="18" thickBot="1">
+    <row r="2" ht="18" thickBot="true">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1892,7 +1895,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3">
       <c r="A3" s="55" t="s">
         <v>10</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>1.2491796243555899</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4">
       <c r="A4" s="65" t="s">
         <v>14</v>
       </c>
@@ -2052,7 +2055,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5">
       <c r="A5" s="65" t="s">
         <v>16</v>
       </c>
@@ -2126,7 +2129,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
@@ -2212,7 +2215,7 @@
         <v>1.28807485160889</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7">
       <c r="A7" s="9" t="s">
         <v>18</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>1.2826059405131001</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8">
       <c r="A8" s="14" t="s">
         <v>19</v>
       </c>
@@ -2385,7 +2388,7 @@
         <v>3.49599673204392E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9">
       <c r="A9" s="14" t="s">
         <v>20</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>3.201694809211E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10">
       <c r="A10" s="9" t="s">
         <v>21</v>
       </c>
@@ -2547,7 +2550,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11">
       <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
@@ -2633,7 +2636,7 @@
         <v>1.22671187197488</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12">
       <c r="A12" s="9" t="s">
         <v>23</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>1.30115536169697</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13">
       <c r="A13" s="9" t="s">
         <v>24</v>
       </c>
@@ -2805,7 +2808,7 @@
         <v>1.3105951770381701</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14">
       <c r="A14" s="9" t="s">
         <v>25</v>
       </c>
@@ -2891,7 +2894,7 @@
         <v>1.3007906732321699</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15">
       <c r="A15" s="9" t="s">
         <v>26</v>
       </c>
@@ -2966,7 +2969,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16">
       <c r="A16" s="65" t="s">
         <v>27</v>
       </c>
@@ -3040,7 +3043,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="17" spans="1:29">
+    <row r="17">
       <c r="A17" s="9" t="s">
         <v>28</v>
       </c>
@@ -3126,7 +3129,7 @@
         <v>1.25315119669604</v>
       </c>
     </row>
-    <row r="18" spans="1:29">
+    <row r="18">
       <c r="A18" s="65" t="s">
         <v>29</v>
       </c>
@@ -3200,7 +3203,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="1:29">
+    <row r="19">
       <c r="A19" s="9" t="s">
         <v>30</v>
       </c>
@@ -3286,7 +3289,7 @@
         <v>1.15022778533231</v>
       </c>
     </row>
-    <row r="20" spans="1:29">
+    <row r="20">
       <c r="A20" s="65" t="s">
         <v>31</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21">
       <c r="A21" s="65" t="s">
         <v>32</v>
       </c>
@@ -3434,7 +3437,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22">
       <c r="A22" s="14" t="s">
         <v>33</v>
       </c>
@@ -3521,7 +3524,7 @@
         <v>7.9507070282666204E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23">
       <c r="A23" s="65" t="s">
         <v>34</v>
       </c>
@@ -3595,7 +3598,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24">
       <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
@@ -3681,7 +3684,7 @@
         <v>1.2101882266169399</v>
       </c>
     </row>
-    <row r="25" spans="1:29">
+    <row r="25">
       <c r="A25" s="65" t="s">
         <v>36</v>
       </c>
@@ -3755,7 +3758,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="1:29">
+    <row r="26">
       <c r="A26" s="9" t="s">
         <v>37</v>
       </c>
@@ -3841,7 +3844,7 @@
         <v>1.16283095851486</v>
       </c>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27">
       <c r="A27" s="65" t="s">
         <v>38</v>
       </c>
@@ -3915,7 +3918,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="28" spans="1:29">
+    <row r="28">
       <c r="A28" s="65" t="s">
         <v>39</v>
       </c>
@@ -3989,7 +3992,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="29" spans="1:29">
+    <row r="29">
       <c r="A29" s="9" t="s">
         <v>40</v>
       </c>
@@ -4075,7 +4078,7 @@
         <v>1.5044176354839999E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:29">
+    <row r="30">
       <c r="A30" s="9" t="s">
         <v>41</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>1.3554316093580201</v>
       </c>
     </row>
-    <row r="31" spans="1:29">
+    <row r="31">
       <c r="A31" s="65" t="s">
         <v>42</v>
       </c>
@@ -4235,7 +4238,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="16" thickBot="1">
+    <row r="32" ht="16" thickBot="true">
       <c r="A32" s="60" t="s">
         <v>43</v>
       </c>
@@ -4310,7 +4313,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33">
       <c r="A33" s="55" t="s">
         <v>44</v>
       </c>
@@ -4396,7 +4399,7 @@
         <v>3.45020994718839</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
@@ -4482,7 +4485,7 @@
         <v>1.99615252466199</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
+    <row r="35">
       <c r="A35" s="9" t="s">
         <v>47</v>
       </c>
@@ -4568,7 +4571,7 @@
         <v>0.85216687949320202</v>
       </c>
     </row>
-    <row r="36" spans="1:29">
+    <row r="36">
       <c r="A36" s="9" t="s">
         <v>48</v>
       </c>
@@ -4654,7 +4657,7 @@
         <v>4.5668445745128299</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37">
       <c r="A37" s="9" t="s">
         <v>49</v>
       </c>
@@ -4740,7 +4743,7 @@
         <v>5282.4123792642004</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38">
       <c r="A38" s="9" t="s">
         <v>50</v>
       </c>
@@ -4826,7 +4829,7 @@
         <v>4.6949101271999298</v>
       </c>
     </row>
-    <row r="39" spans="1:29">
+    <row r="39">
       <c r="A39" s="9" t="s">
         <v>51</v>
       </c>
@@ -4912,7 +4915,7 @@
         <v>6370629.7274044696</v>
       </c>
     </row>
-    <row r="40" spans="1:29">
+    <row r="40">
       <c r="A40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4998,7 +5001,7 @@
         <v>8541334.0303174108</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
+    <row r="41">
       <c r="A41" s="9" t="s">
         <v>53</v>
       </c>
@@ -5084,7 +5087,7 @@
         <v>8476246.4149265904</v>
       </c>
     </row>
-    <row r="42" spans="1:29">
+    <row r="42">
       <c r="A42" s="9" t="s">
         <v>54</v>
       </c>
@@ -5170,7 +5173,7 @@
         <v>7.2839034169655603</v>
       </c>
     </row>
-    <row r="43" spans="1:29">
+    <row r="43">
       <c r="A43" s="9" t="s">
         <v>55</v>
       </c>
@@ -5256,7 +5259,7 @@
         <v>27.7768598766</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
+    <row r="44">
       <c r="A44" s="9" t="s">
         <v>56</v>
       </c>
@@ -5342,7 +5345,7 @@
         <v>2.1371807692417302</v>
       </c>
     </row>
-    <row r="45" spans="1:29">
+    <row r="45">
       <c r="A45" s="9" t="s">
         <v>57</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>12.122672256348899</v>
       </c>
     </row>
-    <row r="46" spans="1:29">
+    <row r="46">
       <c r="A46" s="9" t="s">
         <v>58</v>
       </c>
@@ -5514,7 +5517,7 @@
         <v>4.1563812547059298</v>
       </c>
     </row>
-    <row r="47" spans="1:29">
+    <row r="47">
       <c r="A47" s="9" t="s">
         <v>59</v>
       </c>
@@ -5600,7 +5603,7 @@
         <v>78.849612262011604</v>
       </c>
     </row>
-    <row r="48" spans="1:29">
+    <row r="48">
       <c r="A48" s="65" t="s">
         <v>60</v>
       </c>
@@ -5668,7 +5671,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="49" spans="1:29">
+    <row r="49">
       <c r="A49" s="9" t="s">
         <v>61</v>
       </c>
@@ -5754,7 +5757,7 @@
         <v>1.06055897877955</v>
       </c>
     </row>
-    <row r="50" spans="1:29">
+    <row r="50">
       <c r="A50" s="9" t="s">
         <v>62</v>
       </c>
@@ -5840,7 +5843,7 @@
         <v>1.6379502252846401</v>
       </c>
     </row>
-    <row r="51" spans="1:29">
+    <row r="51">
       <c r="A51" s="9" t="s">
         <v>63</v>
       </c>
@@ -5926,7 +5929,7 @@
         <v>2.7893646620324501</v>
       </c>
     </row>
-    <row r="52" spans="1:29">
+    <row r="52">
       <c r="A52" s="9" t="s">
         <v>64</v>
       </c>
@@ -6012,7 +6015,7 @@
         <v>0.74700365574710703</v>
       </c>
     </row>
-    <row r="53" spans="1:29">
+    <row r="53">
       <c r="A53" s="9" t="s">
         <v>65</v>
       </c>
@@ -6098,7 +6101,7 @@
         <v>1687.45112812361</v>
       </c>
     </row>
-    <row r="54" spans="1:29">
+    <row r="54">
       <c r="A54" s="65" t="s">
         <v>66</v>
       </c>
@@ -6166,7 +6169,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="55" spans="1:29">
+    <row r="55">
       <c r="A55" s="9" t="s">
         <v>67</v>
       </c>
@@ -6252,7 +6255,7 @@
         <v>3.5391218868659302</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="16" thickBot="1">
+    <row r="56" ht="16" thickBot="true">
       <c r="A56" s="60" t="s">
         <v>68</v>
       </c>
@@ -6338,7 +6341,7 @@
         <v>22.381112895193901</v>
       </c>
     </row>
-    <row r="57" spans="1:29">
+    <row r="57">
       <c r="A57" s="26" t="s">
         <v>69</v>
       </c>
@@ -6425,7 +6428,7 @@
         <v>6.3781527468587498E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:29">
+    <row r="58">
       <c r="A58" s="31" t="s">
         <v>71</v>
       </c>
@@ -6512,7 +6515,7 @@
         <v>4.9154700824752999E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:29">
+    <row r="59">
       <c r="A59" s="31" t="s">
         <v>72</v>
       </c>
@@ -6599,7 +6602,7 @@
         <v>5.2316129932117599E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:29">
+    <row r="60">
       <c r="A60" s="31" t="s">
         <v>73</v>
       </c>
@@ -6686,7 +6689,7 @@
         <v>5.4949692364207801E-5</v>
       </c>
     </row>
-    <row r="61" spans="1:29">
+    <row r="61">
       <c r="A61" s="31" t="s">
         <v>74</v>
       </c>
@@ -6773,7 +6776,7 @@
         <v>4.9039352779553004E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:29">
+    <row r="62">
       <c r="A62" s="14" t="s">
         <v>75</v>
       </c>
@@ -6860,7 +6863,7 @@
         <v>3.7440992525965102</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63">
       <c r="A63" s="31" t="s">
         <v>76</v>
       </c>
@@ -6947,7 +6950,7 @@
         <v>0.20469473197330301</v>
       </c>
     </row>
-    <row r="64" spans="1:29">
+    <row r="64">
       <c r="A64" s="14" t="s">
         <v>77</v>
       </c>
@@ -7034,7 +7037,7 @@
         <v>4.3529528977723897E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:29">
+    <row r="65">
       <c r="A65" s="31" t="s">
         <v>78</v>
       </c>
@@ -7121,7 +7124,7 @@
         <v>1.4380246664216301E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:29">
+    <row r="66">
       <c r="A66" s="31" t="s">
         <v>79</v>
       </c>
@@ -7208,7 +7211,7 @@
         <v>8.6040819113413006E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:29">
+    <row r="67">
       <c r="A67" s="14" t="s">
         <v>80</v>
       </c>
@@ -7295,7 +7298,7 @@
         <v>3.49852802989228E-4</v>
       </c>
     </row>
-    <row r="68" spans="1:29">
+    <row r="68">
       <c r="A68" s="14" t="s">
         <v>81</v>
       </c>
@@ -7382,7 +7385,7 @@
         <v>4.3441941491464604</v>
       </c>
     </row>
-    <row r="69" spans="1:29">
+    <row r="69">
       <c r="A69" s="31" t="s">
         <v>82</v>
       </c>
@@ -7469,7 +7472,7 @@
         <v>5.4890252517372502E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:29">
+    <row r="70">
       <c r="A70" s="31" t="s">
         <v>83</v>
       </c>
@@ -7556,7 +7559,7 @@
         <v>5.4133476265916095E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:29">
+    <row r="71">
       <c r="A71" s="31" t="s">
         <v>84</v>
       </c>
@@ -7643,7 +7646,7 @@
         <v>1.0016733323158999E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:29">
+    <row r="72">
       <c r="A72" s="31" t="s">
         <v>85</v>
       </c>
@@ -7730,7 +7733,7 @@
         <v>3.7065183024607003E-4</v>
       </c>
     </row>
-    <row r="73" spans="1:29">
+    <row r="73">
       <c r="A73" s="31" t="s">
         <v>86</v>
       </c>
@@ -7817,7 +7820,7 @@
         <v>3.3949817827852002E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:29">
+    <row r="74">
       <c r="A74" s="31" t="s">
         <v>87</v>
       </c>
@@ -7904,7 +7907,7 @@
         <v>2.0113289099851899E-5</v>
       </c>
     </row>
-    <row r="75" spans="1:29">
+    <row r="75">
       <c r="A75" s="31" t="s">
         <v>88</v>
       </c>
@@ -7991,7 +7994,7 @@
         <v>3.577072928906E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:29">
+    <row r="76">
       <c r="A76" s="31" t="s">
         <v>89</v>
       </c>
@@ -8078,7 +8081,7 @@
         <v>3.1936508506243399E-4</v>
       </c>
     </row>
-    <row r="77" spans="1:29">
+    <row r="77">
       <c r="A77" s="31" t="s">
         <v>90</v>
       </c>
@@ -8165,7 +8168,7 @@
         <v>3.2547110183910001E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:29">
+    <row r="78">
       <c r="A78" s="31" t="s">
         <v>91</v>
       </c>
@@ -8252,7 +8255,7 @@
         <v>3.4476608223003402E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:29">
+    <row r="79">
       <c r="A79" s="31" t="s">
         <v>92</v>
       </c>
@@ -8339,7 +8342,7 @@
         <v>5.3063081099712398E-4</v>
       </c>
     </row>
-    <row r="80" spans="1:29">
+    <row r="80">
       <c r="A80" s="31" t="s">
         <v>93</v>
       </c>
@@ -8426,7 +8429,7 @@
         <v>2.0992032036403001E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:29">
+    <row r="81">
       <c r="A81" s="31" t="s">
         <v>94</v>
       </c>
@@ -8513,7 +8516,7 @@
         <v>6.0792887386858403E-4</v>
       </c>
     </row>
-    <row r="82" spans="1:29">
+    <row r="82">
       <c r="A82" s="31" t="s">
         <v>95</v>
       </c>
@@ -8600,7 +8603,7 @@
         <v>4.1658859483330502E-4</v>
       </c>
     </row>
-    <row r="83" spans="1:29">
+    <row r="83">
       <c r="A83" s="31" t="s">
         <v>96</v>
       </c>
@@ -8687,7 +8690,7 @@
         <v>4.0815389230785902E-4</v>
       </c>
     </row>
-    <row r="84" spans="1:29">
+    <row r="84">
       <c r="A84" s="14" t="s">
         <v>97</v>
       </c>
@@ -8774,7 +8777,7 @@
         <v>3.09988880659623E-4</v>
       </c>
     </row>
-    <row r="85" spans="1:29">
+    <row r="85">
       <c r="A85" s="31" t="s">
         <v>98</v>
       </c>
@@ -8861,7 +8864,7 @@
         <v>4.26934254285498E-4</v>
       </c>
     </row>
-    <row r="86" spans="1:29">
+    <row r="86">
       <c r="A86" s="31" t="s">
         <v>99</v>
       </c>
@@ -8948,7 +8951,7 @@
         <v>3.3142933064940002E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:29">
+    <row r="87">
       <c r="A87" s="31" t="s">
         <v>100</v>
       </c>
@@ -9035,7 +9038,7 @@
         <v>4.1838102676123402E-4</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="16" thickBot="1">
+    <row r="88" ht="16" thickBot="true">
       <c r="A88" s="36" t="s">
         <v>101</v>
       </c>
@@ -9122,7 +9125,7 @@
         <v>3.1487657880199999E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:29">
+    <row r="89">
       <c r="A89" s="55" t="s">
         <v>102</v>
       </c>
@@ -9208,7 +9211,7 @@
         <v>1.3906105107470001E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:29">
+    <row r="90">
       <c r="A90" s="31" t="s">
         <v>104</v>
       </c>
@@ -9295,7 +9298,7 @@
         <v>2.8107310607928999E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:29">
+    <row r="91">
       <c r="A91" s="31" t="s">
         <v>105</v>
       </c>
@@ -9382,7 +9385,7 @@
         <v>1.13462661971E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:29">
+    <row r="92">
       <c r="A92" s="31" t="s">
         <v>106</v>
       </c>
@@ -9469,7 +9472,7 @@
         <v>2.69586660928082E-4</v>
       </c>
     </row>
-    <row r="93" spans="1:29">
+    <row r="93">
       <c r="A93" s="31" t="s">
         <v>107</v>
       </c>
@@ -9556,7 +9559,7 @@
         <v>4.8925648269818002E-4</v>
       </c>
     </row>
-    <row r="94" spans="1:29">
+    <row r="94">
       <c r="A94" s="31" t="s">
         <v>108</v>
       </c>
@@ -9643,7 +9646,7 @@
         <v>1.27526727725156E-4</v>
       </c>
     </row>
-    <row r="95" spans="1:29">
+    <row r="95">
       <c r="A95" s="31" t="s">
         <v>109</v>
       </c>
@@ -9730,7 +9733,7 @@
         <v>1.2432848606849999E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:29">
+    <row r="96">
       <c r="A96" s="31" t="s">
         <v>110</v>
       </c>
@@ -9817,7 +9820,7 @@
         <v>5.3558582094561898E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:29">
+    <row r="97">
       <c r="A97" s="31" t="s">
         <v>111</v>
       </c>
@@ -9904,7 +9907,7 @@
         <v>6.6681267221280595E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:29">
+    <row r="98">
       <c r="A98" s="31" t="s">
         <v>112</v>
       </c>
@@ -9991,7 +9994,7 @@
         <v>1.583560828747E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:29">
+    <row r="99">
       <c r="A99" s="31" t="s">
         <v>113</v>
       </c>
@@ -10078,7 +10081,7 @@
         <v>1.169222003072E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:29">
+    <row r="100">
       <c r="A100" s="31" t="s">
         <v>114</v>
       </c>
@@ -10165,7 +10168,7 @@
         <v>7.9114909770376001E-4</v>
       </c>
     </row>
-    <row r="101" spans="1:29">
+    <row r="101">
       <c r="A101" s="31" t="s">
         <v>115</v>
       </c>
@@ -10252,7 +10255,7 @@
         <v>1.47005912498E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:29">
+    <row r="102">
       <c r="A102" s="65" t="s">
         <v>116</v>
       </c>
@@ -10263,7 +10266,7 @@
         <v>103</v>
       </c>
       <c r="D102" s="66" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="E102" s="66">
         <v>-3137092.2785999998</v>
@@ -10320,7 +10323,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="103" spans="1:29">
+    <row r="103">
       <c r="A103" s="31" t="s">
         <v>117</v>
       </c>
@@ -10407,7 +10410,7 @@
         <v>1.6783935856059999E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:29">
+    <row r="104">
       <c r="A104" s="41" t="s">
         <v>248</v>
       </c>
@@ -10494,7 +10497,7 @@
         <v>1.9208626660463001E-4</v>
       </c>
     </row>
-    <row r="105" spans="1:29">
+    <row r="105">
       <c r="A105" s="31" t="s">
         <v>118</v>
       </c>
@@ -10581,7 +10584,7 @@
         <v>1.6167083108429999E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:29">
+    <row r="106">
       <c r="A106" s="31" t="s">
         <v>119</v>
       </c>
@@ -10668,7 +10671,7 @@
         <v>1.6226497710489999E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:29">
+    <row r="107">
       <c r="A107" s="31" t="s">
         <v>120</v>
       </c>
@@ -10755,7 +10758,7 @@
         <v>1.4002808158060001E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:29">
+    <row r="108">
       <c r="A108" s="31" t="s">
         <v>121</v>
       </c>
@@ -10842,7 +10845,7 @@
         <v>1.115907406152E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:29">
+    <row r="109">
       <c r="A109" s="9" t="s">
         <v>122</v>
       </c>
@@ -10928,7 +10931,7 @@
         <v>1.8487138979449999E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:29">
+    <row r="110">
       <c r="A110" s="31" t="s">
         <v>123</v>
       </c>
@@ -11015,7 +11018,7 @@
         <v>4.2706907652864201E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:29">
+    <row r="111">
       <c r="A111" s="65" t="s">
         <v>124</v>
       </c>
@@ -11026,7 +11029,7 @@
         <v>103</v>
       </c>
       <c r="D111" s="66" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="E111" s="66">
         <v>-3205441.7393</v>
@@ -11083,7 +11086,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="112" spans="1:29">
+    <row r="112">
       <c r="A112" s="31" t="s">
         <v>125</v>
       </c>
@@ -11170,7 +11173,7 @@
         <v>2.55727373603782E-4</v>
       </c>
     </row>
-    <row r="113" spans="1:29">
+    <row r="113">
       <c r="A113" s="31" t="s">
         <v>126</v>
       </c>
@@ -11257,7 +11260,7 @@
         <v>1.1981621072439999E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:29">
+    <row r="114">
       <c r="A114" s="31" t="s">
         <v>127</v>
       </c>
@@ -11344,7 +11347,7 @@
         <v>3.3828847767081199E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:29">
+    <row r="115">
       <c r="A115" s="9" t="s">
         <v>128</v>
       </c>
@@ -11430,7 +11433,7 @@
         <v>2.5727375221769998E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:29">
+    <row r="116">
       <c r="A116" s="31" t="s">
         <v>129</v>
       </c>
@@ -11517,7 +11520,7 @@
         <v>9.3873375033618704E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:29">
+    <row r="117">
       <c r="A117" s="31" t="s">
         <v>130</v>
       </c>
@@ -11604,7 +11607,7 @@
         <v>1.9118863678860001E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:29">
+    <row r="118">
       <c r="A118" s="31" t="s">
         <v>131</v>
       </c>
@@ -11691,7 +11694,7 @@
         <v>1.760923912009E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:29">
+    <row r="119">
       <c r="A119" s="31" t="s">
         <v>132</v>
       </c>
@@ -11778,7 +11781,7 @@
         <v>5.2450442026001295E-4</v>
       </c>
     </row>
-    <row r="120" spans="1:29">
+    <row r="120">
       <c r="A120" s="31" t="s">
         <v>133</v>
       </c>
@@ -11865,7 +11868,7 @@
         <v>1.0313087973529999E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:29">
+    <row r="121">
       <c r="A121" s="31" t="s">
         <v>134</v>
       </c>
@@ -11952,7 +11955,7 @@
         <v>8.9509514635747599E-4</v>
       </c>
     </row>
-    <row r="122" spans="1:29">
+    <row r="122">
       <c r="A122" s="31" t="s">
         <v>135</v>
       </c>
@@ -12039,7 +12042,7 @@
         <v>2.6802360652991699E-4</v>
       </c>
     </row>
-    <row r="123" spans="1:29">
+    <row r="123">
       <c r="A123" s="31" t="s">
         <v>136</v>
       </c>
@@ -12126,7 +12129,7 @@
         <v>1.1433344857660001E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:29">
+    <row r="124">
       <c r="A124" s="65" t="s">
         <v>137</v>
       </c>
@@ -12137,7 +12140,7 @@
         <v>103</v>
       </c>
       <c r="D124" s="66" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="E124" s="66">
         <v>-3044008.6030999999</v>
@@ -12194,7 +12197,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:29">
+    <row r="125">
       <c r="A125" s="31" t="s">
         <v>138</v>
       </c>
@@ -12281,7 +12284,7 @@
         <v>7.0116828155676397E-4</v>
       </c>
     </row>
-    <row r="126" spans="1:29">
+    <row r="126">
       <c r="A126" s="31" t="s">
         <v>139</v>
       </c>
@@ -12368,7 +12371,7 @@
         <v>3.4343367867879798E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:29">
+    <row r="127">
       <c r="A127" s="31" t="s">
         <v>140</v>
       </c>
@@ -12455,7 +12458,7 @@
         <v>3.4335433783422E-4</v>
       </c>
     </row>
-    <row r="128" spans="1:29">
+    <row r="128">
       <c r="A128" s="31" t="s">
         <v>141</v>
       </c>
@@ -12542,7 +12545,7 @@
         <v>2.0864503752989999E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:29">
+    <row r="129">
       <c r="A129" s="31" t="s">
         <v>142</v>
       </c>
@@ -12629,7 +12632,7 @@
         <v>1.748654090373E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:29">
+    <row r="130">
       <c r="A130" s="31" t="s">
         <v>143</v>
       </c>
@@ -12716,7 +12719,7 @@
         <v>1.3439090765369999E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:29">
+    <row r="131">
       <c r="A131" s="31" t="s">
         <v>144</v>
       </c>
@@ -12803,7 +12806,7 @@
         <v>5.0776967190070796E-4</v>
       </c>
     </row>
-    <row r="132" spans="1:29">
+    <row r="132">
       <c r="A132" s="31" t="s">
         <v>145</v>
       </c>
@@ -12890,7 +12893,7 @@
         <v>2.2155015016544301E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:29">
+    <row r="133">
       <c r="A133" s="31" t="s">
         <v>146</v>
       </c>
@@ -12977,7 +12980,7 @@
         <v>5.6474563420216199E-4</v>
       </c>
     </row>
-    <row r="134" spans="1:29">
+    <row r="134">
       <c r="A134" s="9" t="s">
         <v>147</v>
       </c>
@@ -13063,7 +13066,7 @@
         <v>6.9096045849872099E-4</v>
       </c>
     </row>
-    <row r="135" spans="1:29">
+    <row r="135">
       <c r="A135" s="65" t="s">
         <v>148</v>
       </c>
@@ -13074,7 +13077,7 @@
         <v>103</v>
       </c>
       <c r="D135" s="66" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="E135" s="66">
         <v>-3216638.5139000001</v>
@@ -13131,7 +13134,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="136" spans="1:29">
+    <row r="136">
       <c r="A136" s="31" t="s">
         <v>149</v>
       </c>
@@ -13218,7 +13221,7 @@
         <v>6.2758396602806605E-4</v>
       </c>
     </row>
-    <row r="137" spans="1:29">
+    <row r="137">
       <c r="A137" s="31" t="s">
         <v>150</v>
       </c>
@@ -13305,7 +13308,7 @@
         <v>1.632054017381E-3</v>
       </c>
     </row>
-    <row r="138" spans="1:29">
+    <row r="138">
       <c r="A138" s="31" t="s">
         <v>151</v>
       </c>
@@ -13392,7 +13395,7 @@
         <v>1.541036717855E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:29">
+    <row r="139">
       <c r="A139" s="31" t="s">
         <v>152</v>
       </c>
@@ -13479,7 +13482,7 @@
         <v>1.137113617349E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:29">
+    <row r="140">
       <c r="A140" s="31" t="s">
         <v>153</v>
       </c>
@@ -13566,7 +13569,7 @@
         <v>1.6543237031460001E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:29">
+    <row r="141">
       <c r="A141" s="31" t="s">
         <v>154</v>
       </c>
@@ -13653,7 +13656,7 @@
         <v>1.4361521395440001E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:29">
+    <row r="142">
       <c r="A142" s="31" t="s">
         <v>155</v>
       </c>
@@ -13740,7 +13743,7 @@
         <v>1.639332119503E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:29">
+    <row r="143">
       <c r="A143" s="31" t="s">
         <v>156</v>
       </c>
@@ -13827,7 +13830,7 @@
         <v>4.7930289651291802E-4</v>
       </c>
     </row>
-    <row r="144" spans="1:29">
+    <row r="144">
       <c r="A144" s="31" t="s">
         <v>157</v>
       </c>
@@ -13914,7 +13917,7 @@
         <v>3.08256883432761E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:29">
+    <row r="145">
       <c r="A145" s="31" t="s">
         <v>158</v>
       </c>
@@ -14001,7 +14004,7 @@
         <v>5.0166989479458798E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:29">
+    <row r="146">
       <c r="A146" s="31" t="s">
         <v>159</v>
       </c>
@@ -14088,7 +14091,7 @@
         <v>3.2698292839846002E-4</v>
       </c>
     </row>
-    <row r="147" spans="1:29">
+    <row r="147">
       <c r="A147" s="31" t="s">
         <v>160</v>
       </c>
@@ -14175,7 +14178,7 @@
         <v>1.3053050513919999E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:29">
+    <row r="148">
       <c r="A148" s="31" t="s">
         <v>161</v>
       </c>
@@ -14262,7 +14265,7 @@
         <v>2.4693042356208398E-4</v>
       </c>
     </row>
-    <row r="149" spans="1:29">
+    <row r="149">
       <c r="A149" s="31" t="s">
         <v>162</v>
       </c>
@@ -14349,7 +14352,7 @@
         <v>1.9833203447010002E-3</v>
       </c>
     </row>
-    <row r="150" spans="1:29">
+    <row r="150">
       <c r="A150" s="31" t="s">
         <v>163</v>
       </c>
@@ -14436,7 +14439,7 @@
         <v>4.1683404596570004E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:29">
+    <row r="151">
       <c r="A151" s="31" t="s">
         <v>164</v>
       </c>
@@ -14523,7 +14526,7 @@
         <v>1.397011981234E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:29">
+    <row r="152">
       <c r="A152" s="31" t="s">
         <v>165</v>
       </c>
@@ -14610,7 +14613,7 @@
         <v>3.6088731946990003E-4</v>
       </c>
     </row>
-    <row r="153" spans="1:29">
+    <row r="153">
       <c r="A153" s="31" t="s">
         <v>166</v>
       </c>
@@ -14697,7 +14700,7 @@
         <v>4.0612697942199097E-4</v>
       </c>
     </row>
-    <row r="154" spans="1:29">
+    <row r="154">
       <c r="A154" s="31" t="s">
         <v>167</v>
       </c>
@@ -14784,7 +14787,7 @@
         <v>4.1277345020531201E-4</v>
       </c>
     </row>
-    <row r="155" spans="1:29">
+    <row r="155">
       <c r="A155" s="31" t="s">
         <v>168</v>
       </c>
@@ -14871,7 +14874,7 @@
         <v>8.9627114820333602E-4</v>
       </c>
     </row>
-    <row r="156" spans="1:29">
+    <row r="156">
       <c r="A156" s="31" t="s">
         <v>169</v>
       </c>
@@ -14958,7 +14961,7 @@
         <v>1.80899681099424E-4</v>
       </c>
     </row>
-    <row r="157" spans="1:29">
+    <row r="157">
       <c r="A157" s="31" t="s">
         <v>170</v>
       </c>
@@ -15045,7 +15048,7 @@
         <v>1.2383046193539999E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:29">
+    <row r="158">
       <c r="A158" s="31" t="s">
         <v>171</v>
       </c>
@@ -15132,7 +15135,7 @@
         <v>1.876913336634E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:29">
+    <row r="159">
       <c r="A159" s="31" t="s">
         <v>172</v>
       </c>
@@ -15219,7 +15222,7 @@
         <v>1.4476783725849999E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:29">
+    <row r="160">
       <c r="A160" s="9" t="s">
         <v>173</v>
       </c>
@@ -15305,7 +15308,7 @@
         <v>1.325773972033E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:29">
+    <row r="161">
       <c r="A161" s="31" t="s">
         <v>174</v>
       </c>
@@ -15392,7 +15395,7 @@
         <v>3.503407996994E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:29">
+    <row r="162">
       <c r="A162" s="31" t="s">
         <v>175</v>
       </c>
@@ -15479,7 +15482,7 @@
         <v>1.0270326735090001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:29">
+    <row r="163">
       <c r="A163" s="31" t="s">
         <v>176</v>
       </c>
@@ -15566,7 +15569,7 @@
         <v>2.8140797399379999E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:29">
+    <row r="164">
       <c r="A164" s="31" t="s">
         <v>177</v>
       </c>
@@ -15653,7 +15656,7 @@
         <v>1.540466617242E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:29">
+    <row r="165">
       <c r="A165" s="31" t="s">
         <v>178</v>
       </c>
@@ -15740,7 +15743,7 @@
         <v>1.6199862777230001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:29">
+    <row r="166">
       <c r="A166" s="31" t="s">
         <v>179</v>
       </c>
@@ -15827,7 +15830,7 @@
         <v>8.1689043213990103E-4</v>
       </c>
     </row>
-    <row r="167" spans="1:29">
+    <row r="167">
       <c r="A167" s="31" t="s">
         <v>180</v>
       </c>
@@ -15914,7 +15917,7 @@
         <v>7.7819479525917401E-4</v>
       </c>
     </row>
-    <row r="168" spans="1:29">
+    <row r="168">
       <c r="A168" s="31" t="s">
         <v>181</v>
       </c>
@@ -16001,7 +16004,7 @@
         <v>9.3880333642995702E-4</v>
       </c>
     </row>
-    <row r="169" spans="1:29">
+    <row r="169">
       <c r="A169" s="31" t="s">
         <v>182</v>
       </c>
@@ -16088,7 +16091,7 @@
         <v>7.7328724411785402E-5</v>
       </c>
     </row>
-    <row r="170" spans="1:29">
+    <row r="170">
       <c r="A170" s="31" t="s">
         <v>183</v>
       </c>
@@ -16175,7 +16178,7 @@
         <v>1.051317032161E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:29">
+    <row r="171">
       <c r="A171" s="31" t="s">
         <v>184</v>
       </c>
@@ -16262,7 +16265,7 @@
         <v>7.6670411637232497E-4</v>
       </c>
     </row>
-    <row r="172" spans="1:29">
+    <row r="172">
       <c r="A172" s="65" t="s">
         <v>185</v>
       </c>
@@ -16273,7 +16276,7 @@
         <v>103</v>
       </c>
       <c r="D172" s="66" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="E172" s="66">
         <v>-3316134.5712000001</v>
@@ -16330,7 +16333,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="173" spans="1:29">
+    <row r="173">
       <c r="A173" s="31" t="s">
         <v>186</v>
       </c>
@@ -16417,7 +16420,7 @@
         <v>7.1415301277866596E-4</v>
       </c>
     </row>
-    <row r="174" spans="1:29">
+    <row r="174">
       <c r="A174" s="31" t="s">
         <v>187</v>
       </c>
@@ -16504,7 +16507,7 @@
         <v>1.3209637942669999E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:29">
+    <row r="175">
       <c r="A175" s="31" t="s">
         <v>188</v>
       </c>
@@ -16591,7 +16594,7 @@
         <v>6.8631725892694801E-4</v>
       </c>
     </row>
-    <row r="176" spans="1:29">
+    <row r="176">
       <c r="A176" s="31" t="s">
         <v>189</v>
       </c>
@@ -16678,7 +16681,7 @@
         <v>1.29052856305942E-4</v>
       </c>
     </row>
-    <row r="177" spans="1:29">
+    <row r="177">
       <c r="A177" s="31" t="s">
         <v>190</v>
       </c>
@@ -16765,7 +16768,7 @@
         <v>9.1588490099413098E-5</v>
       </c>
     </row>
-    <row r="178" spans="1:29">
+    <row r="178">
       <c r="A178" s="31" t="s">
         <v>191</v>
       </c>
@@ -16852,7 +16855,7 @@
         <v>1.498731395E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:29">
+    <row r="179">
       <c r="A179" s="31" t="s">
         <v>192</v>
       </c>
@@ -16939,7 +16942,7 @@
         <v>8.4697803587733503E-4</v>
       </c>
     </row>
-    <row r="180" spans="1:29">
+    <row r="180">
       <c r="A180" s="31" t="s">
         <v>193</v>
       </c>
@@ -17026,7 +17029,7 @@
         <v>5.3127691525435496E-4</v>
       </c>
     </row>
-    <row r="181" spans="1:29">
+    <row r="181">
       <c r="A181" s="31" t="s">
         <v>194</v>
       </c>
@@ -17113,7 +17116,7 @@
         <v>4.1396128966240801E-4</v>
       </c>
     </row>
-    <row r="182" spans="1:29">
+    <row r="182">
       <c r="A182" s="31" t="s">
         <v>195</v>
       </c>
@@ -17200,7 +17203,7 @@
         <v>6.7752421366272996E-4</v>
       </c>
     </row>
-    <row r="183" spans="1:29">
+    <row r="183">
       <c r="A183" s="31" t="s">
         <v>196</v>
       </c>
@@ -17287,7 +17290,7 @@
         <v>5.7748639161415104E-4</v>
       </c>
     </row>
-    <row r="184" spans="1:29">
+    <row r="184">
       <c r="A184" s="31" t="s">
         <v>197</v>
       </c>
@@ -17374,7 +17377,7 @@
         <v>1.01199305934068E-4</v>
       </c>
     </row>
-    <row r="185" spans="1:29">
+    <row r="185">
       <c r="A185" s="31" t="s">
         <v>198</v>
       </c>
@@ -17461,7 +17464,7 @@
         <v>4.4822294649851299E-4</v>
       </c>
     </row>
-    <row r="186" spans="1:29">
+    <row r="186">
       <c r="A186" s="31" t="s">
         <v>199</v>
       </c>
@@ -17548,7 +17551,7 @@
         <v>92.507455322493499</v>
       </c>
     </row>
-    <row r="187" spans="1:29">
+    <row r="187">
       <c r="A187" s="31" t="s">
         <v>200</v>
       </c>
@@ -17635,7 +17638,7 @@
         <v>1.3208356198430001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:29">
+    <row r="188">
       <c r="A188" s="31" t="s">
         <v>201</v>
       </c>
@@ -17722,7 +17725,7 @@
         <v>2.606388556634E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:29">
+    <row r="189">
       <c r="A189" s="31" t="s">
         <v>202</v>
       </c>
@@ -17809,7 +17812,7 @@
         <v>1.4898157665469999E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:29" ht="16" thickBot="1">
+    <row r="190" ht="16" thickBot="true">
       <c r="A190" s="36" t="s">
         <v>203</v>
       </c>
@@ -17896,7 +17899,7 @@
         <v>4.9614327898184196E-4</v>
       </c>
     </row>
-    <row r="191" spans="1:29">
+    <row r="191">
       <c r="A191" s="26" t="s">
         <v>204</v>
       </c>
@@ -17977,7 +17980,7 @@
         <v>2.87017884157E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:29">
+    <row r="192">
       <c r="A192" s="14" t="s">
         <v>206</v>
       </c>
@@ -18058,7 +18061,7 @@
         <v>1.7697802517246599</v>
       </c>
     </row>
-    <row r="193" spans="1:29">
+    <row r="193">
       <c r="A193" s="31" t="s">
         <v>207</v>
       </c>
@@ -18139,7 +18142,7 @@
         <v>3.0910936115340001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:29">
+    <row r="194">
       <c r="A194" s="31" t="s">
         <v>208</v>
       </c>
@@ -18220,7 +18223,7 @@
         <v>3.0267244760289998E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:29" ht="16" thickBot="1">
+    <row r="195" ht="16" thickBot="true">
       <c r="A195" s="36" t="s">
         <v>209</v>
       </c>
@@ -18301,7 +18304,7 @@
         <v>1.3225508527429999E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:29">
+    <row r="196">
       <c r="A196" s="71" t="s">
         <v>210</v>
       </c>
@@ -18375,7 +18378,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="197" spans="1:29">
+    <row r="197">
       <c r="A197" s="65" t="s">
         <v>212</v>
       </c>
@@ -18449,7 +18452,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="198" spans="1:29">
+    <row r="198">
       <c r="A198" s="65" t="s">
         <v>213</v>
       </c>
@@ -18523,7 +18526,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="199" spans="1:29">
+    <row r="199">
       <c r="A199" s="65" t="s">
         <v>214</v>
       </c>
@@ -18597,7 +18600,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="200" spans="1:29" ht="16" thickBot="1">
+    <row r="200" ht="16" thickBot="true">
       <c r="A200" s="76" t="s">
         <v>215</v>
       </c>
@@ -18671,7 +18674,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="201" spans="1:29">
+    <row r="201">
       <c r="A201" s="55" t="s">
         <v>216</v>
       </c>
@@ -18757,7 +18760,7 @@
         <v>3.7743868430382799</v>
       </c>
     </row>
-    <row r="202" spans="1:29">
+    <row r="202">
       <c r="A202" s="9" t="s">
         <v>218</v>
       </c>
@@ -18843,7 +18846,7 @@
         <v>19.587869785841399</v>
       </c>
     </row>
-    <row r="203" spans="1:29">
+    <row r="203">
       <c r="A203" s="9" t="s">
         <v>219</v>
       </c>
@@ -18929,7 +18932,7 @@
         <v>2.0912071522873101</v>
       </c>
     </row>
-    <row r="204" spans="1:29">
+    <row r="204">
       <c r="A204" s="9" t="s">
         <v>220</v>
       </c>
@@ -19015,7 +19018,7 @@
         <v>3.2239438276988301</v>
       </c>
     </row>
-    <row r="205" spans="1:29">
+    <row r="205">
       <c r="A205" s="9" t="s">
         <v>221</v>
       </c>
@@ -19101,7 +19104,7 @@
         <v>0.41458384332215897</v>
       </c>
     </row>
-    <row r="206" spans="1:29">
+    <row r="206">
       <c r="A206" s="9" t="s">
         <v>222</v>
       </c>
@@ -19187,7 +19190,7 @@
         <v>0.275257798713819</v>
       </c>
     </row>
-    <row r="207" spans="1:29">
+    <row r="207">
       <c r="A207" s="9" t="s">
         <v>223</v>
       </c>
@@ -19273,7 +19276,7 @@
         <v>1.03124495962604</v>
       </c>
     </row>
-    <row r="208" spans="1:29">
+    <row r="208">
       <c r="A208" s="9" t="s">
         <v>224</v>
       </c>
@@ -19359,7 +19362,7 @@
         <v>3.29179776440782</v>
       </c>
     </row>
-    <row r="209" spans="1:29">
+    <row r="209">
       <c r="A209" s="9" t="s">
         <v>225</v>
       </c>
@@ -19445,7 +19448,7 @@
         <v>0.47838080632858998</v>
       </c>
     </row>
-    <row r="210" spans="1:29">
+    <row r="210">
       <c r="A210" s="9" t="s">
         <v>226</v>
       </c>
@@ -19531,7 +19534,7 @@
         <v>12.919500375702199</v>
       </c>
     </row>
-    <row r="211" spans="1:29">
+    <row r="211">
       <c r="A211" s="9" t="s">
         <v>227</v>
       </c>
@@ -19617,7 +19620,7 @@
         <v>2.6922137652670499</v>
       </c>
     </row>
-    <row r="212" spans="1:29">
+    <row r="212">
       <c r="A212" s="9" t="s">
         <v>228</v>
       </c>
@@ -19703,7 +19706,7 @@
         <v>0.30433806305608702</v>
       </c>
     </row>
-    <row r="213" spans="1:29">
+    <row r="213">
       <c r="A213" s="9" t="s">
         <v>229</v>
       </c>
@@ -19789,7 +19792,7 @@
         <v>0.45250162783400499</v>
       </c>
     </row>
-    <row r="214" spans="1:29">
+    <row r="214">
       <c r="A214" s="9" t="s">
         <v>230</v>
       </c>
@@ -19875,7 +19878,7 @@
         <v>0.46336436079116899</v>
       </c>
     </row>
-    <row r="215" spans="1:29">
+    <row r="215">
       <c r="A215" s="65" t="s">
         <v>231</v>
       </c>
@@ -19949,7 +19952,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="216" spans="1:29">
+    <row r="216">
       <c r="A216" s="9" t="s">
         <v>232</v>
       </c>
@@ -20035,7 +20038,7 @@
         <v>0.20350472927931099</v>
       </c>
     </row>
-    <row r="217" spans="1:29">
+    <row r="217">
       <c r="A217" s="9" t="s">
         <v>233</v>
       </c>
@@ -20121,7 +20124,7 @@
         <v>5.5215480479656999E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:29" ht="16" thickBot="1">
+    <row r="218" ht="16" thickBot="true">
       <c r="A218" s="60" t="s">
         <v>234</v>
       </c>
@@ -20207,7 +20210,7 @@
         <v>3.4453894196846599</v>
       </c>
     </row>
-    <row r="219" spans="1:29">
+    <row r="219">
       <c r="A219" s="55" t="s">
         <v>235</v>
       </c>
@@ -20293,7 +20296,7 @@
         <v>1.42747663871576</v>
       </c>
     </row>
-    <row r="220" spans="1:29">
+    <row r="220">
       <c r="A220" s="14" t="s">
         <v>237</v>
       </c>
@@ -20380,7 +20383,7 @@
         <v>0.253952523948416</v>
       </c>
     </row>
-    <row r="221" spans="1:29">
+    <row r="221">
       <c r="A221" s="14" t="s">
         <v>238</v>
       </c>
@@ -20467,7 +20470,7 @@
         <v>1.1463487354783699</v>
       </c>
     </row>
-    <row r="222" spans="1:29">
+    <row r="222">
       <c r="A222" s="9" t="s">
         <v>239</v>
       </c>
@@ -20553,7 +20556,7 @@
         <v>0.26083884171042698</v>
       </c>
     </row>
-    <row r="223" spans="1:29">
+    <row r="223">
       <c r="A223" s="9" t="s">
         <v>240</v>
       </c>
@@ -20639,7 +20642,7 @@
         <v>0.37834020792629502</v>
       </c>
     </row>
-    <row r="224" spans="1:29">
+    <row r="224">
       <c r="A224" s="14" t="s">
         <v>241</v>
       </c>
@@ -20726,7 +20729,7 @@
         <v>0.89328937783509799</v>
       </c>
     </row>
-    <row r="225" spans="1:29">
+    <row r="225">
       <c r="A225" s="9" t="s">
         <v>242</v>
       </c>
@@ -20812,7 +20815,7 @@
         <v>0.28465279944272398</v>
       </c>
     </row>
-    <row r="226" spans="1:29">
+    <row r="226">
       <c r="A226" s="14" t="s">
         <v>243</v>
       </c>
@@ -20899,7 +20902,7 @@
         <v>1.52387017226816</v>
       </c>
     </row>
-    <row r="227" spans="1:29" ht="16" thickBot="1">
+    <row r="227" ht="16" thickBot="true">
       <c r="A227" s="50" t="s">
         <v>244</v>
       </c>
